--- a/riskGenie/NEW資料庫欄位(中英對照).xlsx
+++ b/riskGenie/NEW資料庫欄位(中英對照).xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\riskGenie\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9012" firstSheet="7" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9012" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="1companies" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="209">
   <si>
     <t>assets</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -127,9 +127,6 @@
     <t>department_id</t>
   </si>
   <si>
-    <t>asset_owner</t>
-  </si>
-  <si>
     <t>action</t>
   </si>
   <si>
@@ -261,9 +258,6 @@
   </si>
   <si>
     <t>所屬部門 ID</t>
-  </si>
-  <si>
-    <t>資產擁有者</t>
   </si>
   <si>
     <t>日誌唯一識別碼</t>
@@ -2027,6 +2021,71 @@
       </rPr>
       <t>）</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>department</t>
+  </si>
+  <si>
+    <t>權責單位</t>
+  </si>
+  <si>
+    <t>use_department</t>
+  </si>
+  <si>
+    <t>使用單位</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>放置地點</t>
+  </si>
+  <si>
+    <t>legality</t>
+  </si>
+  <si>
+    <t>適法性 L</t>
+  </si>
+  <si>
+    <t>asset_value</t>
+  </si>
+  <si>
+    <t>upload_user</t>
+  </si>
+  <si>
+    <t>上傳者</t>
+  </si>
+  <si>
+    <t>保管單位(風險擁有者)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UUID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資產價值=CIAL 最大值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前沒使用到 若後續無使用可刪除</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資產的新增 刪除 修改 查詢 都有使用到以下欄位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前資料庫text做測試!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Non-nullable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>risk_owner</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2034,7 +2093,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2176,16 +2235,44 @@
       <family val="3"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -2223,13 +2310,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2244,12 +2366,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2281,9 +2397,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2292,9 +2405,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2313,9 +2423,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2343,6 +2450,51 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2685,96 +2837,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="16">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="16">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="C4" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="19" t="s">
+      <c r="D4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="16">
         <v>3</v>
       </c>
-      <c r="E2" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="19">
-        <v>1</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="19">
-        <v>2</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="B5" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="19">
-        <v>3</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="3"/>
@@ -2791,7 +2943,7 @@
     <row r="11" spans="1:7">
       <c r="A11" s="1"/>
       <c r="C11" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2816,32 +2968,32 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>0</v>
@@ -2849,98 +3001,98 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="12" t="s">
+    <row r="13" spans="1:3">
+      <c r="A13" s="10" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="12" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="12" t="s">
+    <row r="15" spans="1:3">
+      <c r="A15" s="10" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="12" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="9" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="12" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" s="10" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="11" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="12" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="10" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="11" t="s">
+    <row r="20" spans="1:1">
+      <c r="A20" s="10" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="12" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="10" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="12" t="s">
+    <row r="22" spans="1:1">
+      <c r="A22" s="10" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="12" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" s="10" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="12" t="s">
+    <row r="24" spans="1:1">
+      <c r="A24" s="10" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="12" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="9" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="12" t="s">
+    <row r="26" spans="1:1">
+      <c r="A26" s="10" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="12" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2964,102 +3116,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="A1" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="19" t="s">
+      <c r="B2" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="19">
+      <c r="A3" s="16">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="B3" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="16" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="19">
+      <c r="A4" s="16">
         <v>2</v>
       </c>
-      <c r="B4" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="16">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="D5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="19"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="19">
-        <v>3</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+      <c r="A6" s="16">
+        <v>4</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="3"/>
@@ -3102,97 +3269,97 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+        <v>161</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="C2" s="19" t="s">
+      <c r="B2" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:7" ht="16.8" thickBot="1">
-      <c r="A3" s="19">
+      <c r="A3" s="16">
         <v>1</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="65.400000000000006" thickBot="1">
+      <c r="A4" s="16">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="16">
+        <v>3</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="19" t="s">
+      <c r="C5" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="65.400000000000006" thickBot="1">
-      <c r="A4" s="19">
-        <v>2</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="19"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="19">
-        <v>3</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="3"/>
@@ -3222,158 +3389,177 @@
     <col min="7" max="7" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="16"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="16">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="16">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="19" t="s">
+      <c r="C4" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="16">
         <v>3</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="B5" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="16">
         <v>4</v>
       </c>
-      <c r="F2" s="19"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="19">
-        <v>1</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="B6" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="19">
         <v>5</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="19" t="s">
+      <c r="B7" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="19">
-        <v>2</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="19">
-        <v>3</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="19">
-        <v>4</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="23">
-        <v>5</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="19" t="s">
+    <row r="8" spans="1:7">
+      <c r="A8" s="16">
         <v>6</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="B8" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10" s="1"/>
     </row>
-    <row r="11" spans="1:6" ht="19.8">
+    <row r="11" spans="1:7" ht="19.8">
       <c r="A11" s="1"/>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.8">
+      <c r="A12" s="1"/>
+      <c r="B12" s="13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.8">
+      <c r="A13" s="1"/>
+      <c r="B13" s="13" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.8">
-      <c r="A12" s="1"/>
-      <c r="B12" s="15" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="19.8">
-      <c r="A13" s="1"/>
-      <c r="B13" s="15" t="s">
-        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3385,7 +3571,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -3398,427 +3584,526 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.8">
-      <c r="A1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+    </row>
+    <row r="2" spans="1:7" s="42" customFormat="1" ht="36.6">
+      <c r="A2" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="36"/>
+      <c r="B4" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="C4" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="36"/>
+      <c r="B5" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="36"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="36"/>
+      <c r="B6" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="36"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="36"/>
+      <c r="B7" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="C7" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="36"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="36"/>
+      <c r="B8" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="36"/>
+      <c r="B9" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="36"/>
+      <c r="B10" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="36"/>
+      <c r="B11" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="36"/>
+      <c r="B12" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="36"/>
+      <c r="B13" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>208</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+    </row>
+    <row r="14" spans="1:7" ht="14.4" customHeight="1">
+      <c r="A14" s="36"/>
+      <c r="B14" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="36"/>
+      <c r="B15" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="36"/>
+      <c r="B16" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="36"/>
+      <c r="B17" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="36"/>
+      <c r="B18" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="37"/>
+      <c r="B19" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" customHeight="1">
+      <c r="A20" s="36"/>
+      <c r="B20" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="36"/>
+      <c r="B21" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="G21" s="36"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="36"/>
+      <c r="B22" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="B26" s="41"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="38">
         <v>7</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="B27" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="2">
         <v>8</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="B28" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="2">
         <v>12</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="B29" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="2">
         <v>14</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="B30" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="2">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2">
-        <v>10</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="2">
-        <v>12</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="2">
-        <v>13</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="2">
-        <v>14</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="2">
-        <v>15</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="2">
-        <v>16</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="2">
-        <v>17</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="1"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="1"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="1"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="1"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="1"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="1"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="1"/>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1"/>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="1"/>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1"/>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1"/>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="C36" s="1"/>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="1"/>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="1"/>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" s="1"/>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="1"/>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1"/>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="C40" s="1"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="C41" s="1"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="C42" s="1"/>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="1"/>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="1"/>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="1"/>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="1"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="1"/>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1"/>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1"/>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="E2:G2"/>
+  <mergeCells count="3">
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3839,174 +4124,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="A1" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="19" t="s">
+      <c r="A2" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="19">
+      <c r="A3" s="16">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="16">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="16">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="16">
+        <v>4</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="16">
         <v>5</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="B7" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="16">
         <v>6</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="B8" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="16">
         <v>7</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="19">
-        <v>2</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="19" t="s">
+      <c r="B9" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="19"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="19">
-        <v>3</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="19">
-        <v>4</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="19">
-        <v>5</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="19">
-        <v>6</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="19">
-        <v>7</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="4"/>
@@ -4054,235 +4339,235 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C1" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="A1" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="7">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="B7" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" ht="32.4">
+      <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="B8" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="B9" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="B10" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="7">
-        <v>2</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="B11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="7">
-        <v>3</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="F11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="7">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="7">
-        <v>4</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="7">
-        <v>6</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="7">
-        <v>7</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="7">
-        <v>8</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="7">
-        <v>9</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="9">
-        <v>10</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="4"/>
@@ -4326,7 +4611,7 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="8.21875" style="34" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.21875" style="29" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.21875" customWidth="1"/>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
@@ -4336,216 +4621,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="23" t="s">
-        <v>131</v>
+      <c r="A1" s="19" t="s">
+        <v>129</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="C1" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="23" t="s">
+      <c r="B2" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="30">
+      <c r="A3" s="25">
         <v>1</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="14" customFormat="1">
+      <c r="A4" s="25">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="19"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="25">
+        <v>3</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+    </row>
+    <row r="6" spans="1:7" s="14" customFormat="1">
+      <c r="A6" s="25">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="19"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="25">
+        <v>5</v>
+      </c>
+      <c r="B7" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="C7" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="25">
         <v>6</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="B8" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="26">
         <v>7</v>
       </c>
-      <c r="F3" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="23" t="s">
+      <c r="B9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" s="16" customFormat="1">
-      <c r="A4" s="30">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="23"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="30">
-        <v>3</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-    </row>
-    <row r="6" spans="1:7" s="16" customFormat="1">
-      <c r="A6" s="30">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="23"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="30">
-        <v>5</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="30">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="31">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="32"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="32"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="1"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="32"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="1"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="32"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="1"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="32"/>
+      <c r="A14" s="27"/>
       <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="33"/>
+      <c r="A15" s="28"/>
       <c r="B15" s="3"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="33"/>
+      <c r="A16" s="28"/>
       <c r="B16" s="3"/>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="33"/>
+      <c r="A17" s="28"/>
       <c r="B17" s="3"/>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="33"/>
+      <c r="A18" s="28"/>
       <c r="B18" s="3"/>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="33"/>
+      <c r="A19" s="28"/>
       <c r="B19" s="3"/>
     </row>
   </sheetData>
@@ -4562,136 +4847,136 @@
   <dimension ref="A1:A27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="16384" width="9" style="13"/>
+    <col min="1" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="30" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="19.2">
+      <c r="A2" s="31" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="32" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="19.2">
+      <c r="A4" s="31" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="19.2">
-      <c r="A2" s="36" t="s">
+    <row r="5" spans="1:1">
+      <c r="A5" s="12" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="19.2">
+      <c r="A6" s="31" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="37" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="19.2">
-      <c r="A4" s="36" t="s">
+    <row r="7" spans="1:1">
+      <c r="A7" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="12"/>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="30" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="14" t="s">
+    <row r="10" spans="1:1" ht="19.2">
+      <c r="A10" s="31" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="12" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="19.2">
-      <c r="A6" s="36" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="14" t="s">
+    <row r="12" spans="1:1" ht="19.2">
+      <c r="A12" s="31" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="12" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="14"/>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="35" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="19.2">
-      <c r="A10" s="36" t="s">
+    <row r="14" spans="1:1">
+      <c r="A14" s="12"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="30" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="14" t="s">
+    <row r="16" spans="1:1" ht="19.2">
+      <c r="A16" s="31" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="12" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="19.2">
-      <c r="A12" s="36" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="14" t="s">
+    <row r="18" spans="1:1" ht="19.2">
+      <c r="A18" s="31" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="12" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="14"/>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="35" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="19.2">
-      <c r="A16" s="36" t="s">
+    <row r="20" spans="1:1" ht="19.2">
+      <c r="A20" s="31" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="14" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="12" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="19.2">
-      <c r="A18" s="36" t="s">
+    <row r="22" spans="1:1">
+      <c r="A22" s="12"/>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="30" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="14" t="s">
+    <row r="24" spans="1:1" ht="19.2">
+      <c r="A24" s="31" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="12" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="19.2">
-      <c r="A20" s="36" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="14" t="s">
+    <row r="26" spans="1:1" ht="19.2">
+      <c r="A26" s="31" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="12" t="s">
         <v>188</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="14"/>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="35" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="19.2">
-      <c r="A24" s="36" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="14" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="19.2">
-      <c r="A26" s="36" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="14" t="s">
-        <v>190</v>
       </c>
     </row>
   </sheetData>
